--- a/Master/2209r1/2209r1 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/2209r1/2209r1 @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1334,182 +1334,262 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>4.141</v>
+        <v>6.26</v>
       </c>
       <c r="B45" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>5.6912</v>
+        <v>5.6454</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-0.9757</v>
+        <v>-3.1398</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>0.0166</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>3.142</v>
+        <v>5.261</v>
       </c>
       <c r="B46" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>5.7536</v>
+        <v>5.6457</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>-1.1172</v>
+        <v>-3.2773</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>0.0143</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>2.143</v>
+        <v>4.262</v>
       </c>
       <c r="B47" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="D47" s="7" t="n">
-        <v>5.8124</v>
+        <v>5.6468</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>-1.2617</v>
+        <v>-3.4231</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>0.0139</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>1.144</v>
+        <v>1.258</v>
       </c>
       <c r="B48" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>5.8642</v>
+        <v>5.6469</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>-1.4056</v>
+        <v>-3.1221</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.0125</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>7.145</v>
+        <v>4.141</v>
       </c>
       <c r="B49" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>5.9119</v>
+        <v>5.6912</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>-1.299</v>
+        <v>-0.9757</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.0116</v>
+        <v>0.0166</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>6.146</v>
+        <v>3.142</v>
       </c>
       <c r="B50" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C50" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>5.9562</v>
+        <v>5.7536</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>-1.4454</v>
+        <v>-1.1172</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.0103</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>5.147</v>
+        <v>2.143</v>
       </c>
       <c r="B51" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C51" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>5.9975</v>
+        <v>5.8124</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-1.5969</v>
+        <v>-1.2617</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>0.0101</v>
+        <v>0.0139</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
+        <v>1.144</v>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>5.8642</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>-1.4056</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>0.0125</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
+        <v>7.145</v>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>5.9119</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>-1.299</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>0.0116</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n">
+        <v>6.146</v>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>5.9562</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>-1.4454</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>0.0103</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n">
+        <v>5.147</v>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>5.9975</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>-1.5969</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>0.0101</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n">
         <v>4.148</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B56" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C52" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" s="7" t="n">
+      <c r="C56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="7" t="n">
         <v>6.0333</v>
       </c>
-      <c r="E52" s="7" t="n">
+      <c r="E56" s="7" t="n">
         <v>-1.753</v>
       </c>
-      <c r="F52" s="7" t="n">
+      <c r="F56" s="7" t="n">
         <v>0.0086</v>
       </c>
     </row>
-    <row r="54">
-      <c r="E54" s="8" t="inlineStr">
+    <row r="58">
+      <c r="E58" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F54" s="9" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="E55" s="8" t="inlineStr">
+      <c r="F58" s="9" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F55" s="10" t="n">
-        <v>1.5035</v>
+      <c r="F59" s="10" t="n">
+        <v>1.5041</v>
       </c>
     </row>
   </sheetData>
